--- a/考试范围.xlsx
+++ b/考试范围.xlsx
@@ -149,13 +149,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -197,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -205,13 +211,19 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -525,9 +537,9 @@
   <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -538,16 +550,16 @@
       <c r="C1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="2"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="2"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
     </row>
@@ -559,34 +571,34 @@
       <c r="C4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="2"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="2"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="2"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="2"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
     </row>
@@ -598,21 +610,21 @@
       <c r="C9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="2"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="2"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="2"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
     </row>
@@ -624,16 +636,16 @@
       <c r="C13" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="2"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="2"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
     </row>
@@ -645,16 +657,16 @@
       <c r="C16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="2"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="2"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
     </row>
@@ -666,52 +678,52 @@
       <c r="C19" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="2"/>
+      <c r="A20" s="4"/>
       <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="2"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="2"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="2"/>
+      <c r="A23" s="4"/>
       <c r="B23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="2"/>
+      <c r="A24" s="4"/>
       <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="2"/>
+      <c r="A25" s="4"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
     </row>
@@ -723,52 +735,52 @@
       <c r="C26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="2"/>
+      <c r="A27" s="4"/>
       <c r="B27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="2"/>
+      <c r="A28" s="4"/>
       <c r="B28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="2"/>
+      <c r="A29" s="4"/>
       <c r="B29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="2"/>
+      <c r="A30" s="4"/>
       <c r="B30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="2"/>
+      <c r="A31" s="4"/>
       <c r="B31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
-      <c r="A32" s="2"/>
+      <c r="A32" s="4"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
     </row>
@@ -780,164 +792,164 @@
       <c r="C33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
-      <c r="A34" s="2"/>
+      <c r="A34" s="4"/>
       <c r="B34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
-      <c r="A35" s="2"/>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20.25">
+      <c r="A35" s="4"/>
       <c r="B35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
-      <c r="A36" s="2"/>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
+      <c r="A36" s="4"/>
       <c r="B36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
-      <c r="A37" s="2"/>
+      <c r="A37" s="4"/>
       <c r="B37" s="2"/>
       <c r="C37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
-      <c r="A38" s="2"/>
+      <c r="A38" s="4"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="20.25">
       <c r="A39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
-      <c r="A40" s="2"/>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="20.25">
+      <c r="A40" s="4"/>
       <c r="B40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
-      <c r="A41" s="2"/>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="20.25">
+      <c r="A41" s="4"/>
       <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
-      <c r="A42" s="2"/>
+      <c r="A42" s="4"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="20.25">
       <c r="A43" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
-      <c r="A44" s="2"/>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
+      <c r="A44" s="4"/>
       <c r="B44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
-      <c r="A45" s="2"/>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="20.25">
+      <c r="A45" s="4"/>
       <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
-      <c r="A46" s="2"/>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="20.25">
+      <c r="A46" s="4"/>
       <c r="B46" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C46" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
-      <c r="A47" s="2"/>
+      <c r="C46" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="20.25">
+      <c r="A47" s="4"/>
       <c r="B47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
-      <c r="A48" s="2"/>
+      <c r="A48" s="4"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="20.25">
       <c r="A49" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
-      <c r="A50" s="2"/>
+      <c r="C49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="20.25">
+      <c r="A50" s="4"/>
       <c r="B50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
-      <c r="A51" s="2"/>
+      <c r="C50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="20.25">
+      <c r="A51" s="4"/>
       <c r="B51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
-      <c r="A52" s="2"/>
+      <c r="C51" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="20.25">
+      <c r="A52" s="4"/>
       <c r="B52" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
-      <c r="A53" s="5" t="s">
+      <c r="C52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="20.25">
+      <c r="A53" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <f>SUM(C1:C52)</f>
       </c>
     </row>
